--- a/tests/TC-04/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-04/results/timetable_all_departments_even.xlsx
@@ -57,7 +57,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -78,8 +78,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0E0E0"/>
-        <bgColor rgb="00E0E0E0"/>
+        <fgColor rgb="00CDEFEA"/>
+        <bgColor rgb="00CDEFEA"/>
       </patternFill>
     </fill>
     <fill>
@@ -90,8 +90,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E0E0E0"/>
+        <bgColor rgb="00E0E0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD0E6"/>
+        <bgColor rgb="00FFD0E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E1BEE7"/>
         <bgColor rgb="00E1BEE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD6D1"/>
+        <bgColor rgb="00FFD6D1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFDAB3"/>
+        <bgColor rgb="00FFDAB3"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,20 +126,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD0E6"/>
-        <bgColor rgb="00FFD0E6"/>
+        <fgColor rgb="00F0F4C3"/>
+        <bgColor rgb="00F0F4C3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFDAB3"/>
-        <bgColor rgb="00FFDAB3"/>
+        <fgColor rgb="00DFF3D6"/>
+        <bgColor rgb="00DFF3D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CDEFEA"/>
-        <bgColor rgb="00CDEFEA"/>
+        <fgColor rgb="00FFD6D6"/>
+        <bgColor rgb="00FFD6D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -167,14 +191,14 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
@@ -183,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -191,13 +215,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -206,20 +230,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -230,35 +251,62 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -717,7 +765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -861,321 +909,335 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr"/>
-      <c r="D2" s="8" t="inlineStr"/>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>CS208
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>CS407
 LEC
-Room: 113
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="8" t="inlineStr"/>
-      <c r="J2" s="8" t="inlineStr"/>
-      <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="12" t="inlineStr">
+Room: 104
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="10" t="inlineStr"/>
+      <c r="F2" s="10" t="inlineStr"/>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>CS405
+LEC
+Room: 102
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="n"/>
+      <c r="I2" s="12" t="n"/>
+      <c r="J2" s="9" t="n"/>
+      <c r="K2" s="10" t="inlineStr"/>
+      <c r="L2" s="13" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M2" s="13" t="inlineStr">
-        <is>
-          <t>DS151
+      <c r="M2" s="10" t="inlineStr"/>
+      <c r="N2" s="14" t="inlineStr">
+        <is>
+          <t>CS404
+TUT
+Room: 108
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="O2" s="10" t="inlineStr"/>
+      <c r="P2" s="15" t="inlineStr">
+        <is>
+          <t>CS406
 LEC
-Room: 103
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="N2" s="11" t="n"/>
-      <c r="O2" s="8" t="inlineStr"/>
-      <c r="P2" s="8" t="inlineStr"/>
-      <c r="Q2" s="8" t="inlineStr"/>
-      <c r="R2" s="14" t="inlineStr">
-        <is>
-          <t>CS151
+Room: 107
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="Q2" s="12" t="n"/>
+      <c r="R2" s="9" t="n"/>
+      <c r="S2" s="10" t="inlineStr"/>
+      <c r="T2" s="16" t="inlineStr">
+        <is>
+          <t>CS411
+TUT
+Room: 108
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>CS403
+LEC
+Room: 119
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="10" t="inlineStr"/>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>CS401
+LEC
+Room: 104
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="n"/>
+      <c r="H3" s="12" t="n"/>
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="10" t="inlineStr"/>
+      <c r="K3" s="10" t="inlineStr"/>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr"/>
+      <c r="N3" s="19" t="inlineStr">
+        <is>
+          <t>CS402
+LEC
+Room: 108
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="O3" s="12" t="n"/>
+      <c r="P3" s="9" t="n"/>
+      <c r="Q3" s="10" t="inlineStr"/>
+      <c r="R3" s="10" t="inlineStr"/>
+      <c r="S3" s="10" t="inlineStr"/>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>CS407
+TUT
+Room: 117
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>CS404
+LEC
+Room: 111
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="10" t="inlineStr"/>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>CS401
+LEC
+Room: 104
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="n"/>
+      <c r="H4" s="12" t="n"/>
+      <c r="I4" s="9" t="n"/>
+      <c r="J4" s="10" t="inlineStr"/>
+      <c r="K4" s="10" t="inlineStr"/>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
+      <c r="O4" s="19" t="inlineStr">
+        <is>
+          <t>CS402
+TUT
+Room: 116
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="P4" s="12" t="n"/>
+      <c r="Q4" s="9" t="n"/>
+      <c r="R4" s="10" t="inlineStr"/>
+      <c r="S4" s="10" t="inlineStr"/>
+      <c r="T4" s="20" t="inlineStr">
+        <is>
+          <t>CS409
 TUT
 Room: 106
 Dr. Overloaded</t>
         </is>
       </c>
-      <c r="S2" s="11" t="n"/>
-      <c r="T2" s="8" t="inlineStr"/>
-      <c r="U2" s="7" t="inlineStr">
+      <c r="U4" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>CS163
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>CS410
+TUT
+Room: 101
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>CS401
+TUT
+Room: 106
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="10" t="inlineStr"/>
+      <c r="I5" s="10" t="inlineStr"/>
+      <c r="J5" s="22" t="inlineStr">
+        <is>
+          <t>CS408
+TUT
+Room: 101
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr"/>
+      <c r="N5" s="17" t="inlineStr">
+        <is>
+          <t>CS403
 LEC
-Room: 106
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>DS151
+Room: 119
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="n"/>
+      <c r="P5" s="9" t="n"/>
+      <c r="Q5" s="10" t="inlineStr"/>
+      <c r="R5" s="15" t="inlineStr">
+        <is>
+          <t>CS406
+TUT
+Room: 102
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="S5" s="9" t="n"/>
+      <c r="T5" s="10" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>CS404
 LEC
-Room: 103
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="10" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="8" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M3" s="16" t="inlineStr">
-        <is>
-          <t>CS165/CS201
+Room: 111
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="10" t="inlineStr"/>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>CS402
 LEC
 Room: 108
 Dr. Overloaded</t>
         </is>
       </c>
-      <c r="N3" s="11" t="n"/>
-      <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="14" t="inlineStr">
-        <is>
-          <t>CS151
-LEC
-Room: 102
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="11" t="n"/>
-      <c r="S3" s="8" t="inlineStr"/>
-      <c r="T3" s="8" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>CS165/CS201
-LEC
-Room: 108
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="15" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 106
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="10" t="n"/>
-      <c r="I4" s="11" t="n"/>
-      <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr">
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="9" t="n"/>
+      <c r="J6" s="10" t="inlineStr"/>
+      <c r="K6" s="10" t="inlineStr"/>
+      <c r="L6" s="13" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M4" s="17" t="inlineStr">
-        <is>
-          <t>CS162
-LEC
-Room: 116
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="N4" s="11" t="n"/>
-      <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="9" t="inlineStr">
-        <is>
-          <t>CS208
-LEC
-Room: 113
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="11" t="n"/>
-      <c r="S4" s="8" t="inlineStr"/>
-      <c r="T4" s="8" t="inlineStr"/>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 106
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="n"/>
-      <c r="F5" s="10" t="n"/>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="16" t="inlineStr">
-        <is>
-          <t>CS165/CS201
-LEC
-Room: 108
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="N5" s="11" t="n"/>
-      <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="17" t="inlineStr">
-        <is>
-          <t>CS162
-LEC
-Room: 116
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="Q5" s="10" t="n"/>
-      <c r="R5" s="11" t="n"/>
-      <c r="S5" s="8" t="inlineStr"/>
-      <c r="T5" s="13" t="inlineStr">
-        <is>
-          <t>DS151
-TUT
-Room: 101
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 106
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>CS165/CS201
-LEC
-Room: 108
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="8" t="inlineStr"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr"/>
-      <c r="N6" s="17" t="inlineStr">
-        <is>
-          <t>CS162
+      <c r="M6" s="10" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
+      <c r="O6" s="17" t="inlineStr">
+        <is>
+          <t>CS403
 TUT
 Room: 104
 Dr. Overloaded</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr"/>
-      <c r="P6" s="14" t="inlineStr">
-        <is>
-          <t>CS151
-LEC
-Room: 102
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="Q6" s="10" t="n"/>
-      <c r="R6" s="11" t="n"/>
-      <c r="S6" s="8" t="inlineStr"/>
-      <c r="T6" s="18" t="inlineStr">
-        <is>
-          <t>DA151
+      <c r="P6" s="12" t="n"/>
+      <c r="Q6" s="9" t="n"/>
+      <c r="R6" s="10" t="inlineStr"/>
+      <c r="S6" s="10" t="inlineStr"/>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>CS405
 TUT
-Room: 117
+Room: 118
 Dr. Overloaded</t>
         </is>
       </c>
@@ -1186,258 +1248,369 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Course Details</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>Course Code</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>Name of the Course</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>Course Co-ordinator</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>LTPSC</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="24" t="inlineStr">
         <is>
           <t>Room Number</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>CS162</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="inlineStr"/>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>Optimization</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t>116</t>
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>CS401</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr"/>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>Algorithms</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="F12" s="25" t="inlineStr">
+        <is>
+          <t>104</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>CS163</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr"/>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>Data Structures and Algorithms</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>3-0-2-0-4</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>CS402</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr"/>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>Networks</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="F13" s="25" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>CS403</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="inlineStr"/>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="F14" s="25" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>CS404</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="inlineStr"/>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>DBMS</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="F15" s="25" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>CS405</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="inlineStr"/>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="F16" s="25" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>CS406</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr"/>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="F17" s="25" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>CS407</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="inlineStr"/>
+      <c r="C18" s="25" t="inlineStr">
+        <is>
+          <t>Compilers</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="F18" s="25" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>CS408</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="inlineStr"/>
+      <c r="C19" s="25" t="inlineStr">
+        <is>
+          <t>Graphics</t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="F19" s="25" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>CS409</t>
+        </is>
+      </c>
+      <c r="B20" s="34" t="inlineStr"/>
+      <c r="C20" s="25" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D20" s="25" t="inlineStr">
+        <is>
+          <t>Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="F20" s="25" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="21" t="inlineStr">
-        <is>
-          <t>CS208</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="inlineStr"/>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>Computer Architecture</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
-        <is>
-          <t>3-0-2-0-2</t>
-        </is>
-      </c>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="21" t="inlineStr">
-        <is>
-          <t>CS165/CS201</t>
-        </is>
-      </c>
-      <c r="B15" s="25" t="inlineStr"/>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>Mathematical Foundations of Computing/Discrete Mathematics</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
-        <is>
-          <t>3-0-0-0-3</t>
-        </is>
-      </c>
-      <c r="F15" s="21" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>CS410</t>
+        </is>
+      </c>
+      <c r="B21" s="35" t="inlineStr"/>
+      <c r="C21" s="25" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="E21" s="25" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="F21" s="25" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>CS411</t>
+        </is>
+      </c>
+      <c r="B22" s="36" t="inlineStr"/>
+      <c r="C22" s="25" t="inlineStr">
+        <is>
+          <t>Distributed</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="inlineStr">
+        <is>
+          <t>Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="F22" s="25" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="21" t="inlineStr">
-        <is>
-          <t>DS151</t>
-        </is>
-      </c>
-      <c r="B16" s="26" t="inlineStr"/>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>Linux for Engineers</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="21" t="inlineStr">
-        <is>
-          <t>CS151</t>
-        </is>
-      </c>
-      <c r="B17" s="27" t="inlineStr"/>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>Introduction to Cybersecurity</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="F17" s="21" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="21" t="inlineStr">
-        <is>
-          <t>DA151</t>
-        </is>
-      </c>
-      <c r="B18" s="28" t="inlineStr"/>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>Introduction to Financial Analytics</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="M2:N2"/>
+  <mergeCells count="16">
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="E5:G5"/>
     <mergeCell ref="F3:I3"/>
     <mergeCell ref="F4:I4"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="G2:J2"/>
     <mergeCell ref="C3:D3"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="R5:S5"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1451,7 +1624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1595,321 +1768,335 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr"/>
-      <c r="D2" s="8" t="inlineStr"/>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>CS208
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>CS407
 LEC
-Room: 113
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="8" t="inlineStr"/>
-      <c r="J2" s="8" t="inlineStr"/>
-      <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="12" t="inlineStr">
+Room: 104
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="10" t="inlineStr"/>
+      <c r="F2" s="10" t="inlineStr"/>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>CS405
+LEC
+Room: 102
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="n"/>
+      <c r="I2" s="12" t="n"/>
+      <c r="J2" s="9" t="n"/>
+      <c r="K2" s="10" t="inlineStr"/>
+      <c r="L2" s="13" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M2" s="13" t="inlineStr">
-        <is>
-          <t>DS151
+      <c r="M2" s="10" t="inlineStr"/>
+      <c r="N2" s="14" t="inlineStr">
+        <is>
+          <t>CS404
+TUT
+Room: 108
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="O2" s="10" t="inlineStr"/>
+      <c r="P2" s="15" t="inlineStr">
+        <is>
+          <t>CS406
 LEC
-Room: 103
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="N2" s="11" t="n"/>
-      <c r="O2" s="8" t="inlineStr"/>
-      <c r="P2" s="8" t="inlineStr"/>
-      <c r="Q2" s="8" t="inlineStr"/>
-      <c r="R2" s="14" t="inlineStr">
-        <is>
-          <t>CS151
+Room: 107
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="Q2" s="12" t="n"/>
+      <c r="R2" s="9" t="n"/>
+      <c r="S2" s="10" t="inlineStr"/>
+      <c r="T2" s="16" t="inlineStr">
+        <is>
+          <t>CS411
+TUT
+Room: 108
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>CS403
+LEC
+Room: 119
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="10" t="inlineStr"/>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>CS401
+LEC
+Room: 104
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="n"/>
+      <c r="H3" s="12" t="n"/>
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="10" t="inlineStr"/>
+      <c r="K3" s="10" t="inlineStr"/>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr"/>
+      <c r="N3" s="19" t="inlineStr">
+        <is>
+          <t>CS402
+LEC
+Room: 108
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="O3" s="12" t="n"/>
+      <c r="P3" s="9" t="n"/>
+      <c r="Q3" s="10" t="inlineStr"/>
+      <c r="R3" s="10" t="inlineStr"/>
+      <c r="S3" s="10" t="inlineStr"/>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>CS407
+TUT
+Room: 117
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>CS404
+LEC
+Room: 111
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="10" t="inlineStr"/>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>CS401
+LEC
+Room: 104
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="n"/>
+      <c r="H4" s="12" t="n"/>
+      <c r="I4" s="9" t="n"/>
+      <c r="J4" s="10" t="inlineStr"/>
+      <c r="K4" s="10" t="inlineStr"/>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
+      <c r="O4" s="19" t="inlineStr">
+        <is>
+          <t>CS402
+TUT
+Room: 116
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="P4" s="12" t="n"/>
+      <c r="Q4" s="9" t="n"/>
+      <c r="R4" s="10" t="inlineStr"/>
+      <c r="S4" s="10" t="inlineStr"/>
+      <c r="T4" s="20" t="inlineStr">
+        <is>
+          <t>CS409
 TUT
 Room: 106
 Dr. Overloaded</t>
         </is>
       </c>
-      <c r="S2" s="11" t="n"/>
-      <c r="T2" s="8" t="inlineStr"/>
-      <c r="U2" s="7" t="inlineStr">
+      <c r="U4" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>CS163
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>CS410
+TUT
+Room: 101
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr"/>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>CS401
+TUT
+Room: 106
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="10" t="inlineStr"/>
+      <c r="I5" s="10" t="inlineStr"/>
+      <c r="J5" s="22" t="inlineStr">
+        <is>
+          <t>CS408
+TUT
+Room: 101
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr"/>
+      <c r="N5" s="17" t="inlineStr">
+        <is>
+          <t>CS403
 LEC
-Room: 106
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="n"/>
-      <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>DS151
+Room: 119
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="n"/>
+      <c r="P5" s="9" t="n"/>
+      <c r="Q5" s="10" t="inlineStr"/>
+      <c r="R5" s="15" t="inlineStr">
+        <is>
+          <t>CS406
+TUT
+Room: 102
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="S5" s="9" t="n"/>
+      <c r="T5" s="10" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>CS404
 LEC
-Room: 103
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="10" t="n"/>
-      <c r="I3" s="11" t="n"/>
-      <c r="J3" s="8" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M3" s="16" t="inlineStr">
-        <is>
-          <t>CS165/CS201
+Room: 111
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="10" t="inlineStr"/>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>CS402
 LEC
 Room: 108
 Dr. Overloaded</t>
         </is>
       </c>
-      <c r="N3" s="11" t="n"/>
-      <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="14" t="inlineStr">
-        <is>
-          <t>CS151
-LEC
-Room: 102
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="11" t="n"/>
-      <c r="S3" s="8" t="inlineStr"/>
-      <c r="T3" s="8" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>CS165/CS201
-LEC
-Room: 108
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="15" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 106
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="10" t="n"/>
-      <c r="I4" s="11" t="n"/>
-      <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr">
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="9" t="n"/>
+      <c r="J6" s="10" t="inlineStr"/>
+      <c r="K6" s="10" t="inlineStr"/>
+      <c r="L6" s="13" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M4" s="17" t="inlineStr">
-        <is>
-          <t>CS162
-LEC
-Room: 116
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="N4" s="11" t="n"/>
-      <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="9" t="inlineStr">
-        <is>
-          <t>CS208
-LEC
-Room: 113
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="11" t="n"/>
-      <c r="S4" s="8" t="inlineStr"/>
-      <c r="T4" s="8" t="inlineStr"/>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 106
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="n"/>
-      <c r="F5" s="10" t="n"/>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="16" t="inlineStr">
-        <is>
-          <t>CS165/CS201
-LEC
-Room: 108
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="N5" s="11" t="n"/>
-      <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="17" t="inlineStr">
-        <is>
-          <t>CS162
-LEC
-Room: 116
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="Q5" s="10" t="n"/>
-      <c r="R5" s="11" t="n"/>
-      <c r="S5" s="8" t="inlineStr"/>
-      <c r="T5" s="13" t="inlineStr">
-        <is>
-          <t>DS151
-TUT
-Room: 101
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 106
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>CS165/CS201
-LEC
-Room: 108
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="8" t="inlineStr"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr"/>
-      <c r="N6" s="17" t="inlineStr">
-        <is>
-          <t>CS162
+      <c r="M6" s="10" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
+      <c r="O6" s="17" t="inlineStr">
+        <is>
+          <t>CS403
 TUT
 Room: 104
 Dr. Overloaded</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr"/>
-      <c r="P6" s="14" t="inlineStr">
-        <is>
-          <t>CS151
-LEC
-Room: 102
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="Q6" s="10" t="n"/>
-      <c r="R6" s="11" t="n"/>
-      <c r="S6" s="8" t="inlineStr"/>
-      <c r="T6" s="18" t="inlineStr">
-        <is>
-          <t>DA151
+      <c r="P6" s="12" t="n"/>
+      <c r="Q6" s="9" t="n"/>
+      <c r="R6" s="10" t="inlineStr"/>
+      <c r="S6" s="10" t="inlineStr"/>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>CS405
 TUT
-Room: 117
+Room: 118
 Dr. Overloaded</t>
         </is>
       </c>
@@ -1920,258 +2107,369 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Course Details</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>Course Code</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>Name of the Course</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>Course Co-ordinator</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>LTPSC</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="24" t="inlineStr">
         <is>
           <t>Room Number</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>CS162</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="inlineStr"/>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>Optimization</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t>116</t>
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>CS401</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr"/>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>Algorithms</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="F12" s="25" t="inlineStr">
+        <is>
+          <t>104</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>CS163</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr"/>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>Data Structures and Algorithms</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>3-0-2-0-4</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>CS402</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr"/>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>Networks</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="F13" s="25" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>CS403</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="inlineStr"/>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="F14" s="25" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>CS404</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="inlineStr"/>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>DBMS</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="F15" s="25" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>CS405</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="inlineStr"/>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="F16" s="25" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>CS406</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr"/>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="F17" s="25" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>CS407</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="inlineStr"/>
+      <c r="C18" s="25" t="inlineStr">
+        <is>
+          <t>Compilers</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="F18" s="25" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>CS408</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="inlineStr"/>
+      <c r="C19" s="25" t="inlineStr">
+        <is>
+          <t>Graphics</t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="F19" s="25" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>CS409</t>
+        </is>
+      </c>
+      <c r="B20" s="34" t="inlineStr"/>
+      <c r="C20" s="25" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D20" s="25" t="inlineStr">
+        <is>
+          <t>Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="F20" s="25" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="21" t="inlineStr">
-        <is>
-          <t>CS208</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="inlineStr"/>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>Computer Architecture</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
-        <is>
-          <t>3-0-2-0-2</t>
-        </is>
-      </c>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="21" t="inlineStr">
-        <is>
-          <t>CS165/CS201</t>
-        </is>
-      </c>
-      <c r="B15" s="25" t="inlineStr"/>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>Mathematical Foundations of Computing/Discrete Mathematics</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
-        <is>
-          <t>3-0-0-0-3</t>
-        </is>
-      </c>
-      <c r="F15" s="21" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>CS410</t>
+        </is>
+      </c>
+      <c r="B21" s="35" t="inlineStr"/>
+      <c r="C21" s="25" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="E21" s="25" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="F21" s="25" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>CS411</t>
+        </is>
+      </c>
+      <c r="B22" s="36" t="inlineStr"/>
+      <c r="C22" s="25" t="inlineStr">
+        <is>
+          <t>Distributed</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="inlineStr">
+        <is>
+          <t>Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="inlineStr">
+        <is>
+          <t>3-1-0-0-4</t>
+        </is>
+      </c>
+      <c r="F22" s="25" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="21" t="inlineStr">
-        <is>
-          <t>DS151</t>
-        </is>
-      </c>
-      <c r="B16" s="26" t="inlineStr"/>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>Linux for Engineers</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="21" t="inlineStr">
-        <is>
-          <t>CS151</t>
-        </is>
-      </c>
-      <c r="B17" s="27" t="inlineStr"/>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>Introduction to Cybersecurity</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="F17" s="21" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="21" t="inlineStr">
-        <is>
-          <t>DA151</t>
-        </is>
-      </c>
-      <c r="B18" s="28" t="inlineStr"/>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>Introduction to Financial Analytics</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="M2:N2"/>
+  <mergeCells count="16">
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="E5:G5"/>
     <mergeCell ref="F3:I3"/>
     <mergeCell ref="F4:I4"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="G2:J2"/>
     <mergeCell ref="C3:D3"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="R5:S5"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2184,7 +2482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2239,10 +2537,10 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2251,7 +2549,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2261,7 +2559,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CS208</t>
+          <t>CS407</t>
         </is>
       </c>
     </row>
@@ -2275,10 +2573,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2287,7 +2585,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2297,7 +2595,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DS151</t>
+          <t>CS405</t>
         </is>
       </c>
     </row>
@@ -2311,11 +2609,11 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D4" t="n">
         <v>18</v>
       </c>
-      <c r="D4" t="n">
-        <v>19</v>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Dr. Overloaded</t>
@@ -2323,17 +2621,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>107</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CS151</t>
+          <t>CS406</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2657,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2369,7 +2667,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS403</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2693,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2405,7 +2703,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DS151</t>
+          <t>CS401</t>
         </is>
       </c>
     </row>
@@ -2419,10 +2717,10 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2441,7 +2739,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CS165/CS201</t>
+          <t>CS402</t>
         </is>
       </c>
     </row>
@@ -2452,13 +2750,13 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
         <v>3</v>
       </c>
-      <c r="C8" t="n">
-        <v>16</v>
-      </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2467,7 +2765,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>111</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2477,7 +2775,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CS151</t>
+          <t>CS404</t>
         </is>
       </c>
     </row>
@@ -2491,10 +2789,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2503,7 +2801,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2513,7 +2811,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CS165/CS201</t>
+          <t>CS401</t>
         </is>
       </c>
     </row>
@@ -2527,10 +2825,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2539,17 +2837,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>116</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS402</t>
         </is>
       </c>
     </row>
@@ -2560,13 +2858,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2575,17 +2873,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>106</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>CS401</t>
         </is>
       </c>
     </row>
@@ -2596,13 +2894,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2611,17 +2909,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CS208</t>
+          <t>CS408</t>
         </is>
       </c>
     </row>
@@ -2635,10 +2933,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2647,7 +2945,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2657,7 +2955,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS403</t>
         </is>
       </c>
     </row>
@@ -2671,10 +2969,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2683,17 +2981,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CS165/CS201</t>
+          <t>CS406</t>
         </is>
       </c>
     </row>
@@ -2704,13 +3002,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2719,7 +3017,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>111</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2729,7 +3027,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>CS404</t>
         </is>
       </c>
     </row>
@@ -2743,10 +3041,10 @@
         <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -2755,7 +3053,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>108</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2765,7 +3063,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS402</t>
         </is>
       </c>
     </row>
@@ -2779,10 +3077,10 @@
         <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -2791,34 +3089,34 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>CS165/CS201</t>
+          <t>CS403</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CSE_4_A</t>
+          <t>CSE_4_B</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -2827,7 +3125,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2837,7 +3135,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>CS151</t>
+          <t>CS407</t>
         </is>
       </c>
     </row>
@@ -2851,10 +3149,10 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -2863,7 +3161,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2873,7 +3171,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CS208</t>
+          <t>CS405</t>
         </is>
       </c>
     </row>
@@ -2887,10 +3185,10 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -2899,7 +3197,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>107</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2909,7 +3207,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>DS151</t>
+          <t>CS406</t>
         </is>
       </c>
     </row>
@@ -2920,13 +3218,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -2935,17 +3233,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CS151</t>
+          <t>CS403</t>
         </is>
       </c>
     </row>
@@ -2959,10 +3257,10 @@
         <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -2971,7 +3269,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2981,7 +3279,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS401</t>
         </is>
       </c>
     </row>
@@ -2995,10 +3293,10 @@
         <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -3007,7 +3305,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>108</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3017,7 +3315,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>DS151</t>
+          <t>CS402</t>
         </is>
       </c>
     </row>
@@ -3028,13 +3326,13 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="n">
         <v>3</v>
       </c>
-      <c r="C24" t="n">
-        <v>13</v>
-      </c>
       <c r="D24" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -3043,7 +3341,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>111</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3053,7 +3351,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>CS165/CS201</t>
+          <t>CS404</t>
         </is>
       </c>
     </row>
@@ -3064,13 +3362,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -3079,7 +3377,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3089,7 +3387,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>CS151</t>
+          <t>CS401</t>
         </is>
       </c>
     </row>
@@ -3103,10 +3401,10 @@
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -3115,17 +3413,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>116</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>CS165/CS201</t>
+          <t>CS402</t>
         </is>
       </c>
     </row>
@@ -3136,13 +3434,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -3156,12 +3454,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS401</t>
         </is>
       </c>
     </row>
@@ -3172,13 +3470,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -3187,17 +3485,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>CS408</t>
         </is>
       </c>
     </row>
@@ -3208,14 +3506,14 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
+        <v>14</v>
+      </c>
+      <c r="D29" t="n">
         <v>16</v>
       </c>
-      <c r="D29" t="n">
-        <v>18</v>
-      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>Dr. Overloaded</t>
@@ -3223,7 +3521,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3233,7 +3531,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>CS208</t>
+          <t>CS403</t>
         </is>
       </c>
     </row>
@@ -3247,10 +3545,10 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -3259,17 +3557,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS406</t>
         </is>
       </c>
     </row>
@@ -3280,13 +3578,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -3295,7 +3593,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>111</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3305,7 +3603,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CS165/CS201</t>
+          <t>CS404</t>
         </is>
       </c>
     </row>
@@ -3316,13 +3614,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -3331,7 +3629,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>108</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3341,7 +3639,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>CS402</t>
         </is>
       </c>
     </row>
@@ -3355,10 +3653,10 @@
         <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -3367,89 +3665,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>CS163</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>CSE_4_B</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>6</v>
-      </c>
-      <c r="C34" t="n">
-        <v>6</v>
-      </c>
-      <c r="D34" t="n">
-        <v>9</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>LEC</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>CS165/CS201</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>CSE_4_B</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>6</v>
-      </c>
-      <c r="C35" t="n">
-        <v>16</v>
-      </c>
-      <c r="D35" t="n">
-        <v>18</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>LEC</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>CS151</t>
+          <t>CS403</t>
         </is>
       </c>
     </row>

--- a/tests/TC-04/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-04/results/timetable_all_departments_even.xlsx
@@ -78,20 +78,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CDEFEA"/>
-        <bgColor rgb="00CDEFEA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3BF"/>
-        <bgColor rgb="00FFF3BF"/>
+        <fgColor rgb="00C8E6C9"/>
+        <bgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E0E0E0"/>
         <bgColor rgb="00E0E0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFDAB3"/>
+        <bgColor rgb="00FFDAB3"/>
       </patternFill>
     </fill>
     <fill>
@@ -108,26 +108,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD6D1"/>
-        <bgColor rgb="00FFD6D1"/>
+        <fgColor rgb="00FFF3BF"/>
+        <bgColor rgb="00FFF3BF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFDAB3"/>
-        <bgColor rgb="00FFDAB3"/>
+        <fgColor rgb="00FFD6D6"/>
+        <bgColor rgb="00FFD6D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
-        <bgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00CDEFEA"/>
+        <bgColor rgb="00CDEFEA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F4C3"/>
-        <bgColor rgb="00F0F4C3"/>
+        <fgColor rgb="00FFD6D1"/>
+        <bgColor rgb="00FFD6D1"/>
       </patternFill>
     </fill>
     <fill>
@@ -138,8 +138,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD6D6"/>
-        <bgColor rgb="00FFD6D6"/>
+        <fgColor rgb="00F0F4C3"/>
+        <bgColor rgb="00F0F4C3"/>
       </patternFill>
     </fill>
     <fill>
@@ -230,17 +230,20 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -249,9 +252,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -276,10 +276,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -288,25 +288,25 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -911,24 +911,24 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>CS407
+          <t>CS403
 LEC
-Room: 104
+Room: 113
 Dr. Overloaded</t>
         </is>
       </c>
       <c r="D2" s="9" t="n"/>
       <c r="E2" s="10" t="inlineStr"/>
       <c r="F2" s="10" t="inlineStr"/>
-      <c r="G2" s="11" t="inlineStr">
-        <is>
-          <t>CS405
-LEC
-Room: 102
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="H2" s="12" t="n"/>
+      <c r="G2" s="10" t="inlineStr"/>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>CS402
+TUT
+Room: 119
+Dr. Overloaded</t>
+        </is>
+      </c>
       <c r="I2" s="12" t="n"/>
       <c r="J2" s="9" t="n"/>
       <c r="K2" s="10" t="inlineStr"/>
@@ -938,66 +938,59 @@
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" s="14" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr"/>
+      <c r="O2" s="14" t="inlineStr">
+        <is>
+          <t>CS401
+TUT
+Room: 114
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="P2" s="12" t="n"/>
+      <c r="Q2" s="9" t="n"/>
+      <c r="R2" s="10" t="inlineStr"/>
+      <c r="S2" s="10" t="inlineStr"/>
+      <c r="T2" s="15" t="inlineStr">
         <is>
           <t>CS404
 TUT
-Room: 108
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="O2" s="10" t="inlineStr"/>
-      <c r="P2" s="15" t="inlineStr">
+Room: 119
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>CS406
 LEC
-Room: 107
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="Q2" s="12" t="n"/>
-      <c r="R2" s="9" t="n"/>
-      <c r="S2" s="10" t="inlineStr"/>
-      <c r="T2" s="16" t="inlineStr">
-        <is>
-          <t>CS411
-TUT
-Room: 108
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="U2" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
-        <is>
-          <t>CS403
+Room: 110
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="10" t="inlineStr"/>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>CS405
 LEC
 Room: 119
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="10" t="inlineStr"/>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>CS401
-LEC
-Room: 104
 Dr. Overloaded</t>
         </is>
       </c>
@@ -1012,11 +1005,11 @@
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr"/>
-      <c r="N3" s="19" t="inlineStr">
+      <c r="N3" s="11" t="inlineStr">
         <is>
           <t>CS402
 LEC
-Room: 108
+Room: 114
 Dr. Overloaded</t>
         </is>
       </c>
@@ -1025,42 +1018,152 @@
       <c r="Q3" s="10" t="inlineStr"/>
       <c r="R3" s="10" t="inlineStr"/>
       <c r="S3" s="10" t="inlineStr"/>
-      <c r="T3" s="8" t="inlineStr">
+      <c r="T3" s="18" t="inlineStr">
+        <is>
+          <t>CS408
+TUT
+Room: 107
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>CS407
 TUT
-Room: 117
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="U3" s="7" t="inlineStr">
+Room: 106
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr"/>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>CS402
+LEC
+Room: 114
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="12" t="n"/>
+      <c r="H4" s="9" t="n"/>
+      <c r="I4" s="10" t="inlineStr"/>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>CS411
+TUT
+Room: 114
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="n"/>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="17" t="inlineStr">
+        <is>
+          <t>CS405
+LEC
+Room: 119
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="N4" s="9" t="n"/>
+      <c r="O4" s="10" t="inlineStr"/>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t>CS403
+LEC
+Room: 113
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="Q4" s="12" t="n"/>
+      <c r="R4" s="9" t="n"/>
+      <c r="S4" s="10" t="inlineStr"/>
+      <c r="T4" s="21" t="inlineStr">
+        <is>
+          <t>CS410
+TUT
+Room: 105
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="U4" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>CS404
 LEC
-Room: 111
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="10" t="inlineStr"/>
-      <c r="F4" s="18" t="inlineStr">
+Room: 109
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="10" t="inlineStr"/>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>CS406
+LEC
+Room: 110
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="9" t="n"/>
+      <c r="J5" s="10" t="inlineStr"/>
+      <c r="K5" s="10" t="inlineStr"/>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr"/>
+      <c r="N5" s="17" t="inlineStr">
+        <is>
+          <t>CS405
+TUT
+Room: 106
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="O5" s="10" t="inlineStr"/>
+      <c r="P5" s="10" t="inlineStr"/>
+      <c r="Q5" s="14" t="inlineStr">
         <is>
           <t>CS401
 LEC
@@ -1068,110 +1171,7 @@
 Dr. Overloaded</t>
         </is>
       </c>
-      <c r="G4" s="12" t="n"/>
-      <c r="H4" s="12" t="n"/>
-      <c r="I4" s="9" t="n"/>
-      <c r="J4" s="10" t="inlineStr"/>
-      <c r="K4" s="10" t="inlineStr"/>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="10" t="inlineStr"/>
-      <c r="N4" s="10" t="inlineStr"/>
-      <c r="O4" s="19" t="inlineStr">
-        <is>
-          <t>CS402
-TUT
-Room: 116
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="P4" s="12" t="n"/>
-      <c r="Q4" s="9" t="n"/>
-      <c r="R4" s="10" t="inlineStr"/>
-      <c r="S4" s="10" t="inlineStr"/>
-      <c r="T4" s="20" t="inlineStr">
-        <is>
-          <t>CS409
-TUT
-Room: 106
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>CS410
-TUT
-Room: 101
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr"/>
-      <c r="E5" s="18" t="inlineStr">
-        <is>
-          <t>CS401
-TUT
-Room: 106
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="9" t="n"/>
-      <c r="H5" s="10" t="inlineStr"/>
-      <c r="I5" s="10" t="inlineStr"/>
-      <c r="J5" s="22" t="inlineStr">
-        <is>
-          <t>CS408
-TUT
-Room: 101
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="n"/>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr"/>
-      <c r="N5" s="17" t="inlineStr">
-        <is>
-          <t>CS403
-LEC
-Room: 119
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="O5" s="12" t="n"/>
-      <c r="P5" s="9" t="n"/>
-      <c r="Q5" s="10" t="inlineStr"/>
-      <c r="R5" s="15" t="inlineStr">
-        <is>
-          <t>CS406
-TUT
-Room: 102
-Dr. Overloaded</t>
-        </is>
-      </c>
+      <c r="R5" s="12" t="n"/>
       <c r="S5" s="9" t="n"/>
       <c r="T5" s="10" t="inlineStr"/>
       <c r="U5" s="7" t="inlineStr">
@@ -1191,56 +1191,63 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>CS406
+TUT
+Room: 109
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr"/>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>CS401
+LEC
+Room: 104
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="9" t="n"/>
+      <c r="I6" s="10" t="inlineStr"/>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>CS409
+TUT
+Room: 104
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="n"/>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr"/>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>CS403
+TUT
+Room: 113
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="O6" s="10" t="inlineStr"/>
+      <c r="P6" s="10" t="inlineStr"/>
+      <c r="Q6" s="15" t="inlineStr">
         <is>
           <t>CS404
 LEC
-Room: 111
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n"/>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>CS402
-LEC
-Room: 108
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="n"/>
-      <c r="H6" s="12" t="n"/>
-      <c r="I6" s="9" t="n"/>
-      <c r="J6" s="10" t="inlineStr"/>
-      <c r="K6" s="10" t="inlineStr"/>
-      <c r="L6" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" s="10" t="inlineStr"/>
-      <c r="O6" s="17" t="inlineStr">
-        <is>
-          <t>CS403
-TUT
-Room: 104
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="P6" s="12" t="n"/>
-      <c r="Q6" s="9" t="n"/>
-      <c r="R6" s="10" t="inlineStr"/>
-      <c r="S6" s="10" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr">
-        <is>
-          <t>CS405
-TUT
-Room: 118
-Dr. Overloaded</t>
-        </is>
-      </c>
+Room: 109
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="R6" s="12" t="n"/>
+      <c r="S6" s="9" t="n"/>
+      <c r="T6" s="10" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1338,7 +1345,7 @@
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>114</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1373,7 @@
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>113</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1401,7 @@
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>109</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1429,7 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>119</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1457,7 @@
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>110</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1485,7 @@
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>106</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1513,7 @@
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>107</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1541,7 @@
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>104</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1569,7 @@
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>105</t>
         </is>
       </c>
     </row>
@@ -1590,28 +1597,28 @@
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>114</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="Q5:S5"/>
     <mergeCell ref="C2:D2"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="J6:K6"/>
     <mergeCell ref="F3:I3"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="F5:I5"/>
     <mergeCell ref="C3:D3"/>
+    <mergeCell ref="O2:Q2"/>
     <mergeCell ref="N3:P3"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="Q6:S6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1770,24 +1777,24 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>CS407
+          <t>CS403
 LEC
-Room: 104
+Room: 113
 Dr. Overloaded</t>
         </is>
       </c>
       <c r="D2" s="9" t="n"/>
       <c r="E2" s="10" t="inlineStr"/>
       <c r="F2" s="10" t="inlineStr"/>
-      <c r="G2" s="11" t="inlineStr">
-        <is>
-          <t>CS405
-LEC
-Room: 102
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="H2" s="12" t="n"/>
+      <c r="G2" s="10" t="inlineStr"/>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>CS402
+TUT
+Room: 119
+Dr. Overloaded</t>
+        </is>
+      </c>
       <c r="I2" s="12" t="n"/>
       <c r="J2" s="9" t="n"/>
       <c r="K2" s="10" t="inlineStr"/>
@@ -1797,66 +1804,59 @@
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" s="14" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr"/>
+      <c r="O2" s="14" t="inlineStr">
+        <is>
+          <t>CS401
+TUT
+Room: 114
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="P2" s="12" t="n"/>
+      <c r="Q2" s="9" t="n"/>
+      <c r="R2" s="10" t="inlineStr"/>
+      <c r="S2" s="10" t="inlineStr"/>
+      <c r="T2" s="15" t="inlineStr">
         <is>
           <t>CS404
 TUT
-Room: 108
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="O2" s="10" t="inlineStr"/>
-      <c r="P2" s="15" t="inlineStr">
+Room: 119
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>CS406
 LEC
-Room: 107
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="Q2" s="12" t="n"/>
-      <c r="R2" s="9" t="n"/>
-      <c r="S2" s="10" t="inlineStr"/>
-      <c r="T2" s="16" t="inlineStr">
-        <is>
-          <t>CS411
-TUT
-Room: 108
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="U2" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
-        <is>
-          <t>CS403
+Room: 110
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="10" t="inlineStr"/>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>CS405
 LEC
 Room: 119
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="10" t="inlineStr"/>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>CS401
-LEC
-Room: 104
 Dr. Overloaded</t>
         </is>
       </c>
@@ -1871,11 +1871,11 @@
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr"/>
-      <c r="N3" s="19" t="inlineStr">
+      <c r="N3" s="11" t="inlineStr">
         <is>
           <t>CS402
 LEC
-Room: 108
+Room: 114
 Dr. Overloaded</t>
         </is>
       </c>
@@ -1884,42 +1884,152 @@
       <c r="Q3" s="10" t="inlineStr"/>
       <c r="R3" s="10" t="inlineStr"/>
       <c r="S3" s="10" t="inlineStr"/>
-      <c r="T3" s="8" t="inlineStr">
+      <c r="T3" s="18" t="inlineStr">
+        <is>
+          <t>CS408
+TUT
+Room: 107
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>CS407
 TUT
-Room: 117
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="U3" s="7" t="inlineStr">
+Room: 106
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr"/>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>CS402
+LEC
+Room: 114
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="12" t="n"/>
+      <c r="H4" s="9" t="n"/>
+      <c r="I4" s="10" t="inlineStr"/>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>CS411
+TUT
+Room: 114
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="n"/>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="17" t="inlineStr">
+        <is>
+          <t>CS405
+LEC
+Room: 119
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="N4" s="9" t="n"/>
+      <c r="O4" s="10" t="inlineStr"/>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t>CS403
+LEC
+Room: 113
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="Q4" s="12" t="n"/>
+      <c r="R4" s="9" t="n"/>
+      <c r="S4" s="10" t="inlineStr"/>
+      <c r="T4" s="21" t="inlineStr">
+        <is>
+          <t>CS410
+TUT
+Room: 105
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="U4" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>CS404
 LEC
-Room: 111
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="10" t="inlineStr"/>
-      <c r="F4" s="18" t="inlineStr">
+Room: 109
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="10" t="inlineStr"/>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>CS406
+LEC
+Room: 110
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="9" t="n"/>
+      <c r="J5" s="10" t="inlineStr"/>
+      <c r="K5" s="10" t="inlineStr"/>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr"/>
+      <c r="N5" s="17" t="inlineStr">
+        <is>
+          <t>CS405
+TUT
+Room: 106
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="O5" s="10" t="inlineStr"/>
+      <c r="P5" s="10" t="inlineStr"/>
+      <c r="Q5" s="14" t="inlineStr">
         <is>
           <t>CS401
 LEC
@@ -1927,110 +2037,7 @@
 Dr. Overloaded</t>
         </is>
       </c>
-      <c r="G4" s="12" t="n"/>
-      <c r="H4" s="12" t="n"/>
-      <c r="I4" s="9" t="n"/>
-      <c r="J4" s="10" t="inlineStr"/>
-      <c r="K4" s="10" t="inlineStr"/>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="10" t="inlineStr"/>
-      <c r="N4" s="10" t="inlineStr"/>
-      <c r="O4" s="19" t="inlineStr">
-        <is>
-          <t>CS402
-TUT
-Room: 116
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="P4" s="12" t="n"/>
-      <c r="Q4" s="9" t="n"/>
-      <c r="R4" s="10" t="inlineStr"/>
-      <c r="S4" s="10" t="inlineStr"/>
-      <c r="T4" s="20" t="inlineStr">
-        <is>
-          <t>CS409
-TUT
-Room: 106
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>CS410
-TUT
-Room: 101
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr"/>
-      <c r="E5" s="18" t="inlineStr">
-        <is>
-          <t>CS401
-TUT
-Room: 106
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="9" t="n"/>
-      <c r="H5" s="10" t="inlineStr"/>
-      <c r="I5" s="10" t="inlineStr"/>
-      <c r="J5" s="22" t="inlineStr">
-        <is>
-          <t>CS408
-TUT
-Room: 101
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="n"/>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr"/>
-      <c r="N5" s="17" t="inlineStr">
-        <is>
-          <t>CS403
-LEC
-Room: 119
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="O5" s="12" t="n"/>
-      <c r="P5" s="9" t="n"/>
-      <c r="Q5" s="10" t="inlineStr"/>
-      <c r="R5" s="15" t="inlineStr">
-        <is>
-          <t>CS406
-TUT
-Room: 102
-Dr. Overloaded</t>
-        </is>
-      </c>
+      <c r="R5" s="12" t="n"/>
       <c r="S5" s="9" t="n"/>
       <c r="T5" s="10" t="inlineStr"/>
       <c r="U5" s="7" t="inlineStr">
@@ -2050,56 +2057,63 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>CS406
+TUT
+Room: 109
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr"/>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>CS401
+LEC
+Room: 104
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="9" t="n"/>
+      <c r="I6" s="10" t="inlineStr"/>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>CS409
+TUT
+Room: 104
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="n"/>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr"/>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>CS403
+TUT
+Room: 113
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="O6" s="10" t="inlineStr"/>
+      <c r="P6" s="10" t="inlineStr"/>
+      <c r="Q6" s="15" t="inlineStr">
         <is>
           <t>CS404
 LEC
-Room: 111
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n"/>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>CS402
-LEC
-Room: 108
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="n"/>
-      <c r="H6" s="12" t="n"/>
-      <c r="I6" s="9" t="n"/>
-      <c r="J6" s="10" t="inlineStr"/>
-      <c r="K6" s="10" t="inlineStr"/>
-      <c r="L6" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" s="10" t="inlineStr"/>
-      <c r="O6" s="17" t="inlineStr">
-        <is>
-          <t>CS403
-TUT
-Room: 104
-Dr. Overloaded</t>
-        </is>
-      </c>
-      <c r="P6" s="12" t="n"/>
-      <c r="Q6" s="9" t="n"/>
-      <c r="R6" s="10" t="inlineStr"/>
-      <c r="S6" s="10" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr">
-        <is>
-          <t>CS405
-TUT
-Room: 118
-Dr. Overloaded</t>
-        </is>
-      </c>
+Room: 109
+Dr. Overloaded</t>
+        </is>
+      </c>
+      <c r="R6" s="12" t="n"/>
+      <c r="S6" s="9" t="n"/>
+      <c r="T6" s="10" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -2197,7 +2211,7 @@
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>114</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2239,7 @@
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>113</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2267,7 @@
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>109</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2295,7 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>119</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2323,7 @@
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>110</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2351,7 @@
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>106</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2379,7 @@
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>107</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2407,7 @@
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>104</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2435,7 @@
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>105</t>
         </is>
       </c>
     </row>
@@ -2449,28 +2463,28 @@
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>114</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="Q5:S5"/>
     <mergeCell ref="C2:D2"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="J6:K6"/>
     <mergeCell ref="F3:I3"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="F5:I5"/>
     <mergeCell ref="C3:D3"/>
+    <mergeCell ref="O2:Q2"/>
     <mergeCell ref="N3:P3"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="Q6:S6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2549,7 +2563,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2559,7 +2573,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CS407</t>
+          <t>CS403</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2587,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
@@ -2585,17 +2599,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CS405</t>
+          <t>CS402</t>
         </is>
       </c>
     </row>
@@ -2609,10 +2623,10 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2621,17 +2635,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CS406</t>
+          <t>CS401</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2671,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2667,7 +2681,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CS403</t>
+          <t>CS406</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2707,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2703,7 +2717,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CS401</t>
+          <t>CS405</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2743,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2753,10 +2767,10 @@
         <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2765,7 +2779,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2775,7 +2789,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CS404</t>
+          <t>CS402</t>
         </is>
       </c>
     </row>
@@ -2789,10 +2803,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2801,17 +2815,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CS401</t>
+          <t>CS411</t>
         </is>
       </c>
     </row>
@@ -2825,10 +2839,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2837,17 +2851,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CS402</t>
+          <t>CS405</t>
         </is>
       </c>
     </row>
@@ -2858,13 +2872,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2873,17 +2887,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CS401</t>
+          <t>CS403</t>
         </is>
       </c>
     </row>
@@ -2897,10 +2911,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2909,17 +2923,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CS408</t>
+          <t>CS404</t>
         </is>
       </c>
     </row>
@@ -2933,10 +2947,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2945,7 +2959,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2955,7 +2969,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CS403</t>
+          <t>CS406</t>
         </is>
       </c>
     </row>
@@ -2969,7 +2983,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D14" t="n">
         <v>19</v>
@@ -2981,17 +2995,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CS406</t>
+          <t>CS401</t>
         </is>
       </c>
     </row>
@@ -3005,10 +3019,10 @@
         <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -3017,7 +3031,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3027,7 +3041,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CS404</t>
+          <t>CS401</t>
         </is>
       </c>
     </row>
@@ -3041,10 +3055,10 @@
         <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3053,17 +3067,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>CS402</t>
+          <t>CS409</t>
         </is>
       </c>
     </row>
@@ -3077,10 +3091,10 @@
         <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -3089,17 +3103,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>CS403</t>
+          <t>CS404</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3139,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3135,7 +3149,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>CS407</t>
+          <t>CS403</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3163,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -3161,17 +3175,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CS405</t>
+          <t>CS402</t>
         </is>
       </c>
     </row>
@@ -3185,10 +3199,10 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -3197,17 +3211,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>CS406</t>
+          <t>CS401</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3247,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3243,7 +3257,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CS403</t>
+          <t>CS406</t>
         </is>
       </c>
     </row>
@@ -3269,7 +3283,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3279,7 +3293,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>CS401</t>
+          <t>CS405</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3319,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3329,10 +3343,10 @@
         <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -3341,7 +3355,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3351,7 +3365,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>CS404</t>
+          <t>CS402</t>
         </is>
       </c>
     </row>
@@ -3365,10 +3379,10 @@
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -3377,17 +3391,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>CS401</t>
+          <t>CS411</t>
         </is>
       </c>
     </row>
@@ -3401,10 +3415,10 @@
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D26" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -3413,17 +3427,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>CS402</t>
+          <t>CS405</t>
         </is>
       </c>
     </row>
@@ -3434,13 +3448,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -3449,17 +3463,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>CS401</t>
+          <t>CS403</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3487,10 @@
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -3485,17 +3499,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>CS408</t>
+          <t>CS404</t>
         </is>
       </c>
     </row>
@@ -3509,10 +3523,10 @@
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -3521,7 +3535,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3531,7 +3545,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>CS403</t>
+          <t>CS406</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3559,7 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D30" t="n">
         <v>19</v>
@@ -3557,17 +3571,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>CS406</t>
+          <t>CS401</t>
         </is>
       </c>
     </row>
@@ -3581,10 +3595,10 @@
         <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -3593,7 +3607,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3603,7 +3617,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CS404</t>
+          <t>CS401</t>
         </is>
       </c>
     </row>
@@ -3617,10 +3631,10 @@
         <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D32" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -3629,17 +3643,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>CS402</t>
+          <t>CS409</t>
         </is>
       </c>
     </row>
@@ -3653,10 +3667,10 @@
         <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D33" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -3665,17 +3679,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>CS403</t>
+          <t>CS404</t>
         </is>
       </c>
     </row>
